--- a/ALL/p12-out/START.xlsx
+++ b/ALL/p12-out/START.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Titles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Titles" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Classic Vegetable Stir Fry</t>
+          <t>One-Pan Honey Butter Salmon &amp; Rice</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-30 07:25:37</t>
+          <t>2026-05-08 14:43:34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -461,7 +461,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chocolate Banana Pancakes</t>
+          <t>Juicy Air Fryer BBQ Chicken Bites</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -469,12 +469,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-30 07:13:11</t>
+          <t>2026-05-08 14:43:34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>New site (p12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Healthy Greek Chicken Bowls</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Soft &amp; Fluffy Homemade Cinnamon Rolls</t>
         </is>
       </c>
     </row>

--- a/ALL/p12-out/START.xlsx
+++ b/ALL/p12-out/START.xlsx
@@ -484,11 +484,37 @@
           <t>Healthy Greek Chicken Bowls</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-05-08 21:36:21</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New site (p12)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>Soft &amp; Fluffy Homemade Cinnamon Rolls</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-05-08 21:36:21</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New site (p12)</t>
         </is>
       </c>
     </row>
